--- a/output/laminas_comunales/comunal_s_fonasa_a_2021_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2021_valparaiso.xlsx
@@ -375,181 +375,181 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Petorca</t>
         </is>
       </c>
       <c r="C2">
-        <v>252657</v>
+        <v>93.10622858294698</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Viña del Mar</t>
+          <t>Santa María</t>
         </is>
       </c>
       <c r="C3">
-        <v>246545</v>
+        <v>92.16392551311677</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quilpué</t>
+          <t>Catemu</t>
         </is>
       </c>
       <c r="C4">
-        <v>126395</v>
+        <v>92.03694963252646</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Villa Alemana</t>
+          <t>Isla de Pascua</t>
         </is>
       </c>
       <c r="C5">
-        <v>100120</v>
+        <v>91.75335255044492</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Juan Fernández</t>
         </is>
       </c>
       <c r="C6">
-        <v>85144</v>
+        <v>91.10122358175751</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quillota</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="C7">
-        <v>79429</v>
+        <v>91.0641627543036</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>San Felipe</t>
+          <t>Putaendo</t>
         </is>
       </c>
       <c r="C8">
-        <v>69269</v>
+        <v>90.915258069987</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Panquehue</t>
         </is>
       </c>
       <c r="C9">
-        <v>53474</v>
+        <v>90.88644112247574</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Limache</t>
+          <t>Hijuelas</t>
         </is>
       </c>
       <c r="C10">
-        <v>43764</v>
+        <v>90.1803417996412</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>La Ligua</t>
+          <t>Cabildo</t>
         </is>
       </c>
       <c r="C11">
-        <v>35735</v>
+        <v>89.81154013855918</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Concón</t>
+          <t>La Ligua</t>
         </is>
       </c>
       <c r="C12">
-        <v>29372</v>
+        <v>89.59059342642966</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Quintero</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="C13">
-        <v>27739</v>
+        <v>88.21841164585815</v>
       </c>
     </row>
     <row r="14">
@@ -564,352 +564,352 @@
         </is>
       </c>
       <c r="C14">
-        <v>25108</v>
+        <v>86.50175704540757</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Papudo</t>
         </is>
       </c>
       <c r="C15">
-        <v>23276</v>
+        <v>85.94771241830065</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nogales</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="C16">
-        <v>19591</v>
+        <v>85.83838308735145</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hijuelas</t>
+          <t>Puchuncaví</t>
         </is>
       </c>
       <c r="C17">
-        <v>19102</v>
+        <v>85.76408517052948</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cabildo</t>
+          <t>El Quisco</t>
         </is>
       </c>
       <c r="C18">
-        <v>18538</v>
+        <v>85.63242342154615</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Puchuncaví</t>
+          <t>El Tabo</t>
         </is>
       </c>
       <c r="C19">
-        <v>18206</v>
+        <v>85.58679421371909</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>5405</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>La Cruz</t>
+          <t>Zapallar</t>
         </is>
       </c>
       <c r="C20">
-        <v>17680</v>
+        <v>85.52815262912983</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Olmué</t>
+          <t>Nogales</t>
         </is>
       </c>
       <c r="C21">
-        <v>16569</v>
+        <v>85.29322129827159</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>El Quisco</t>
+          <t>Calle Larga</t>
         </is>
       </c>
       <c r="C22">
-        <v>16438</v>
+        <v>85.18952715904651</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Putaendo</t>
+          <t>Olmué</t>
         </is>
       </c>
       <c r="C23">
-        <v>16082</v>
+        <v>84.76926225314642</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>San Esteban</t>
+          <t>Limache</t>
         </is>
       </c>
       <c r="C24">
-        <v>16003</v>
+        <v>84.08876933422999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>El Tabo</t>
+          <t>San Esteban</t>
         </is>
       </c>
       <c r="C25">
-        <v>14673</v>
+        <v>84.0758642429337</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Algarrobo</t>
+          <t>Quintero</t>
         </is>
       </c>
       <c r="C26">
-        <v>13799</v>
+        <v>83.94818872378416</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Catemu</t>
+          <t>Quillota</t>
         </is>
       </c>
       <c r="C27">
-        <v>13650</v>
+        <v>83.69404872292</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Santa María</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="C28">
-        <v>13561</v>
+        <v>82.16380925126177</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Calle Larga</t>
+          <t>Rinconada</t>
         </is>
       </c>
       <c r="C29">
-        <v>13080</v>
+        <v>81.85299336882413</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Petorca</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="C30">
-        <v>9238</v>
+        <v>79.97547223427007</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
+          <t>Villa Alemana</t>
         </is>
       </c>
       <c r="C31">
-        <v>9075</v>
+        <v>78.63033063692767</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rinconada</t>
+          <t>Algarrobo</t>
         </is>
       </c>
       <c r="C32">
-        <v>8764</v>
+        <v>78.28775672302281</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Zapallar</t>
+          <t>Quilpué</t>
         </is>
       </c>
       <c r="C33">
-        <v>7352</v>
+        <v>77.12514415772227</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5201</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Isla de Pascua</t>
+          <t>Santo Domingo</t>
         </is>
       </c>
       <c r="C34">
-        <v>7321</v>
+        <v>74.336500655308</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Panquehue</t>
+          <t>Viña del Mar</t>
         </is>
       </c>
       <c r="C35">
-        <v>6931</v>
+        <v>73.54151876532457</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Papudo</t>
+          <t>La Cruz</t>
         </is>
       </c>
       <c r="C36">
-        <v>5786</v>
+        <v>73.53185825985693</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Juan Fernández</t>
+          <t>Concón</t>
         </is>
       </c>
       <c r="C37">
-        <v>819</v>
+        <v>62.0487145361979</v>
       </c>
     </row>
   </sheetData>
@@ -965,7 +965,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
